--- a/reports/二级子公司D_利润表_2025-07.xlsx
+++ b/reports/二级子公司D_利润表_2025-07.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>92620841</v>
+        <v>95038472</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>90559339</v>
+        <v>90978028</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>563153217</v>
+        <v>563755012</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>312866</v>
+        <v>311719</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1942534</v>
+        <v>1943534</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>269886</v>
+        <v>267339</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1666639</v>
+        <v>1665558</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>222817</v>
+        <v>223123</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1386843</v>
+        <v>1387695</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>202795</v>
+        <v>201256</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1250386</v>
+        <v>1248731</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>111339</v>
+        <v>112090</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>693334</v>
+        <v>693679</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>90067</v>
+        <v>89884</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>555676</v>
+        <v>554938</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>91411071</v>
+        <v>93833061</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>89349569</v>
+        <v>89772617</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>5038870</v>
+        <v>5069271</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>31227712</v>
+        <v>31228085</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>391304</v>
+        <v>393834</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2428391</v>
+        <v>2429338</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>674403</v>
+        <v>673832</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>4166274</v>
+        <v>4165311</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>80239111</v>
+        <v>80663756</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>499290269</v>
+        <v>499897446</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1351801</v>
+        <v>1341058</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>8335708</v>
+        <v>8331989</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>445321</v>
+        <v>446079</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2773317</v>
+        <v>2777217</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2252274</v>
+        <v>2227384</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>13892461</v>
+        <v>13884456</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>557559</v>
+        <v>556648</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3467476</v>
+        <v>3470508</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2021535</v>
+        <v>2005346</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>12497936</v>
+        <v>12491337</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>39967</v>
+        <v>39854</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>279955</v>
+        <v>280006</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1207929</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>7492267</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>807315</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>4994450</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>60696372</v>
+        <v>65713041</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>54451236</v>
+        <v>55094278</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>53437494</v>
+        <v>54080518</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>332798341</v>
+        <v>333044220</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1013742</v>
+        <v>1013760</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>6251805</v>
+        <v>6245785</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2024992</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>12494056</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>646682</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3998777</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>403183</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2499514</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>482630</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2999513</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>361241</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2249521</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>240532</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1499492</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>200400</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1249352</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>946328</v>
+        <v>947129</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5893365</v>
+        <v>5898528</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>732263</v>
+        <v>725538</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>4515292</v>
+        <v>4509796</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>557149</v>
+        <v>559412</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>3467086</v>
+        <v>3468590</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4271959</v>
+        <v>4262233</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>26388692</v>
+        <v>26359482</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>149702</v>
+        <v>168625</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1049665</v>
+        <v>1040520</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>319998</v>
+        <v>321704</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2240082</v>
+        <v>2239179</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>360718</v>
+        <v>321704</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2520625</v>
+        <v>2239179</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>39850</v>
+        <v>40224</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>279859</v>
+        <v>279943</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>162685</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1133924</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>353544</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2186873</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>107959</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>756173</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>80773</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>567185</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>134361</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>945348</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>501062</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3123871</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>71575</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>504131</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>53734</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>378049</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>89721</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>629986</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>62955</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>440925</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>45081</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>314909</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>36143</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>251909</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27148</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>188932</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>30714699</v>
+        <v>29316266</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>35219779</v>
+        <v>32661999</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>202403</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1249467</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>45081</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>315034</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>69807</v>
+        <v>69950</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>489824</v>
+        <v>490119</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>30644892</v>
+        <v>29448719</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2486291</v>
+        <v>2487670</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>17486591</v>
+        <v>17506456</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>28158601</v>
+        <v>26961049</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>28158601</v>
+        <v>26961049</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>28158601</v>
+        <v>26961049</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>28158601</v>
+        <v>26961049</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>28158601</v>
+        <v>26961049</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
